--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -62,6 +62,9 @@
     <t>Nu+100</t>
   </si>
   <si>
+    <t>AddActor</t>
+  </si>
+  <si>
     <t>選択仲間加入</t>
   </si>
   <si>
@@ -110,7 +113,7 @@
     <t>LearnSkill</t>
   </si>
   <si>
-    <t>Numinos</t>
+    <t>Currency</t>
   </si>
   <si>
     <t>Demigod</t>
@@ -119,22 +122,22 @@
     <t>Rebirth</t>
   </si>
   <si>
+    <t>LevelUp</t>
+  </si>
+  <si>
+    <t>StatusUp</t>
+  </si>
+  <si>
+    <t>Regene</t>
+  </si>
+  <si>
+    <t>バトルボーナス</t>
+  </si>
+  <si>
+    <t>SelectRelic</t>
+  </si>
+  <si>
     <t>Ending</t>
-  </si>
-  <si>
-    <t>StatusUp</t>
-  </si>
-  <si>
-    <t>Regene</t>
-  </si>
-  <si>
-    <t>AddActor</t>
-  </si>
-  <si>
-    <t>バトルボーナス</t>
-  </si>
-  <si>
-    <t>SelectRelic</t>
   </si>
 </sst>
 </file>
@@ -142,10 +145,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -158,17 +161,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -193,14 +196,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -208,9 +203,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,6 +218,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -232,39 +233,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,6 +264,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -292,9 +280,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -306,6 +309,18 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -321,13 +336,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -339,7 +354,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -351,43 +366,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,25 +378,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,7 +396,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,13 +426,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,13 +450,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -483,13 +492,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -505,20 +508,39 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -534,6 +556,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -555,48 +595,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -608,145 +611,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1076,7 +1079,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1282,13 +1285,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>252</v>
+        <v>110</v>
       </c>
       <c r="B13">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1299,13 +1302,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>1011</v>
+        <v>252</v>
       </c>
       <c r="B14">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1319,35 +1322,32 @@
         <v>1011</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>1011</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
         <v>11010</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>1031</v>
-      </c>
-      <c r="B16">
-        <v>61</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1356,39 +1356,39 @@
         <v>1031</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" t="s">
         <v>19</v>
-      </c>
-      <c r="F17" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B18">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1396,149 +1396,152 @@
         <v>1032</v>
       </c>
       <c r="B19">
+        <v>61</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>1032</v>
+      </c>
+      <c r="B20">
         <v>71</v>
       </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
         <v>10</v>
       </c>
-      <c r="E19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="E20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>1041</v>
+      </c>
+      <c r="B21">
+        <v>61</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="1">
+        <v>1041</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>12010</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>1041</v>
-      </c>
-      <c r="B20">
-        <v>61</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="1">
-        <v>1041</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>12010</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
+    <row r="23" spans="1:5">
+      <c r="A23">
         <v>1042</v>
       </c>
-      <c r="B22">
-        <v>61</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="1">
+      <c r="B23">
+        <v>61</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1">
         <v>1042</v>
       </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
         <v>13010</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
         <v>1051</v>
       </c>
-      <c r="B24">
-        <v>61</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="1">
+      <c r="B25">
+        <v>61</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1">
         <v>1051</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
         <v>14050</v>
       </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
         <v>1052</v>
       </c>
-      <c r="B26">
-        <v>61</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="1">
-        <v>1052</v>
-      </c>
       <c r="B27">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C27">
-        <v>15010</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1549,56 +1552,53 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1">
+        <v>1052</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>15010</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1">
         <v>1101</v>
       </c>
-      <c r="B28">
-        <v>61</v>
-      </c>
-      <c r="C28">
+      <c r="B29">
+        <v>61</v>
+      </c>
+      <c r="C29">
         <v>4</v>
       </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
         <v>1101</v>
       </c>
-      <c r="B29">
-        <v>2</v>
-      </c>
-      <c r="C29">
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30">
         <v>20</v>
       </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>2041</v>
-      </c>
-      <c r="B30">
-        <v>61</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1606,39 +1606,39 @@
         <v>2041</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C31">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B32">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1646,19 +1646,19 @@
         <v>2042</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C33">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1666,36 +1666,39 @@
         <v>2042</v>
       </c>
       <c r="B34">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D34">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E34" t="s">
         <v>20</v>
       </c>
       <c r="F34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>2042</v>
+      </c>
+      <c r="B35">
+        <v>71</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>2101</v>
-      </c>
-      <c r="B35">
-        <v>61</v>
-      </c>
-      <c r="C35">
-        <v>4</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35" t="s">
-        <v>16</v>
+      <c r="F35" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1703,33 +1706,33 @@
         <v>2101</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C36">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="B37">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1737,16 +1740,16 @@
         <v>2102</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C38">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1754,16 +1757,16 @@
         <v>2102</v>
       </c>
       <c r="B39">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1771,7 +1774,7 @@
         <v>2102</v>
       </c>
       <c r="B40">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C40">
         <v>5</v>
@@ -1785,19 +1788,19 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>3041</v>
+        <v>2102</v>
       </c>
       <c r="B41">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1805,33 +1808,33 @@
         <v>3041</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C42">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="B43">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1839,16 +1842,16 @@
         <v>3042</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C44">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1856,13 +1859,13 @@
         <v>3042</v>
       </c>
       <c r="B45">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D45">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E45" t="s">
         <v>20</v>
@@ -1870,19 +1873,19 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>3101</v>
+        <v>3042</v>
       </c>
       <c r="B46">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1890,33 +1893,33 @@
         <v>3101</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C47">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="B48">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1924,16 +1927,16 @@
         <v>3102</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C49">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1941,16 +1944,16 @@
         <v>3102</v>
       </c>
       <c r="B50">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1958,7 +1961,7 @@
         <v>3102</v>
       </c>
       <c r="B51">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C51">
         <v>5</v>
@@ -1972,19 +1975,19 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>4041</v>
+        <v>3102</v>
       </c>
       <c r="B52">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1992,33 +1995,33 @@
         <v>4041</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C53">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="B54">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2026,16 +2029,16 @@
         <v>4042</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C55">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2043,13 +2046,13 @@
         <v>4042</v>
       </c>
       <c r="B56">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D56">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E56" t="s">
         <v>20</v>
@@ -2057,19 +2060,19 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>4101</v>
+        <v>4042</v>
       </c>
       <c r="B57">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E57" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2077,33 +2080,33 @@
         <v>4101</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C58">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="B59">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2111,16 +2114,16 @@
         <v>4102</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C60">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2128,16 +2131,16 @@
         <v>4102</v>
       </c>
       <c r="B61">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2145,7 +2148,7 @@
         <v>4102</v>
       </c>
       <c r="B62">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C62">
         <v>5</v>
@@ -2159,19 +2162,19 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>5041</v>
+        <v>4102</v>
       </c>
       <c r="B63">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2179,33 +2182,33 @@
         <v>5041</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C64">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>5042</v>
+        <v>5041</v>
       </c>
       <c r="B65">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2213,16 +2216,16 @@
         <v>5042</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C66">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2230,13 +2233,13 @@
         <v>5042</v>
       </c>
       <c r="B67">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D67">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E67" t="s">
         <v>20</v>
@@ -2244,19 +2247,19 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>5101</v>
+        <v>5042</v>
       </c>
       <c r="B68">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C68">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E68" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2264,33 +2267,33 @@
         <v>5101</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C69">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="B70">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2298,16 +2301,16 @@
         <v>5102</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C71">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2315,16 +2318,16 @@
         <v>5102</v>
       </c>
       <c r="B72">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2332,7 +2335,7 @@
         <v>5102</v>
       </c>
       <c r="B73">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C73">
         <v>5</v>
@@ -2346,19 +2349,19 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="B74">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2366,33 +2369,33 @@
         <v>6021</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C75">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="B76">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2400,33 +2403,33 @@
         <v>6022</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C77">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="B78">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2434,16 +2437,16 @@
         <v>6031</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C79">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2451,13 +2454,13 @@
         <v>6031</v>
       </c>
       <c r="B80">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D80">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E80" t="s">
         <v>20</v>
@@ -2465,19 +2468,19 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="B81">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C81">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E81" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2485,33 +2488,33 @@
         <v>6101</v>
       </c>
       <c r="B82">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>11020</v>
+        <v>6101</v>
       </c>
       <c r="B83">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2519,10 +2522,10 @@
         <v>11020</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C84">
-        <v>11020</v>
+        <v>1</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -2533,19 +2536,19 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="B85">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>11020</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2553,10 +2556,10 @@
         <v>11030</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C86">
-        <v>11030</v>
+        <v>1</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2567,19 +2570,19 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>11040</v>
+        <v>11030</v>
       </c>
       <c r="B87">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>11030</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2587,10 +2590,10 @@
         <v>11040</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C88">
-        <v>11040</v>
+        <v>1</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -2601,19 +2604,19 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>12020</v>
+        <v>11040</v>
       </c>
       <c r="B89">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>11040</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2621,10 +2624,10 @@
         <v>12020</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C90">
-        <v>12020</v>
+        <v>1</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -2635,19 +2638,19 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>12030</v>
+        <v>12020</v>
       </c>
       <c r="B91">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>12020</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2655,10 +2658,10 @@
         <v>12030</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C92">
-        <v>12030</v>
+        <v>1</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -2669,19 +2672,19 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>12040</v>
+        <v>12030</v>
       </c>
       <c r="B93">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>12030</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2689,10 +2692,10 @@
         <v>12040</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C94">
-        <v>12040</v>
+        <v>1</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -2703,19 +2706,19 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>13020</v>
+        <v>12040</v>
       </c>
       <c r="B95">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>12040</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2723,10 +2726,10 @@
         <v>13020</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C96">
-        <v>13020</v>
+        <v>1</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -2737,19 +2740,19 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>13030</v>
+        <v>13020</v>
       </c>
       <c r="B97">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>13020</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2757,10 +2760,10 @@
         <v>13030</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C98">
-        <v>13030</v>
+        <v>1</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -2771,19 +2774,19 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>13040</v>
+        <v>13030</v>
       </c>
       <c r="B99">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>13030</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2791,10 +2794,10 @@
         <v>13040</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C100">
-        <v>13040</v>
+        <v>1</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -2805,19 +2808,19 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>14010</v>
+        <v>13040</v>
       </c>
       <c r="B101">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>13040</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2825,10 +2828,10 @@
         <v>14010</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C102">
-        <v>14010</v>
+        <v>1</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -2839,19 +2842,19 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103">
-        <v>14020</v>
+        <v>14010</v>
       </c>
       <c r="B103">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>14010</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2859,10 +2862,10 @@
         <v>14020</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C104">
-        <v>14020</v>
+        <v>1</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -2873,19 +2876,19 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="B105">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>14020</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2893,10 +2896,10 @@
         <v>14030</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C106">
-        <v>14030</v>
+        <v>1</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -2907,19 +2910,19 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>15020</v>
+        <v>14030</v>
       </c>
       <c r="B107">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>14030</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2927,10 +2930,10 @@
         <v>15020</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C108">
-        <v>15020</v>
+        <v>1</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -2941,19 +2944,19 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109">
-        <v>15030</v>
+        <v>15020</v>
       </c>
       <c r="B109">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>15020</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2961,10 +2964,10 @@
         <v>15030</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C110">
-        <v>15030</v>
+        <v>1</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -2975,19 +2978,19 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111">
-        <v>15050</v>
+        <v>15030</v>
       </c>
       <c r="B111">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>15030</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2995,10 +2998,10 @@
         <v>15050</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C112">
-        <v>15050</v>
+        <v>1</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3009,27 +3012,27 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113">
-        <v>20010</v>
+        <v>15050</v>
       </c>
       <c r="B113">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>15050</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B114">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -3043,10 +3046,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115">
-        <v>20030</v>
+        <v>20020</v>
       </c>
       <c r="B115">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -3060,10 +3063,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116">
-        <v>20040</v>
+        <v>20030</v>
       </c>
       <c r="B116">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -3073,6 +3076,23 @@
       </c>
       <c r="E116" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117">
+        <v>20040</v>
+      </c>
+      <c r="B117">
+        <v>104</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3084,12 +3104,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3097,7 +3117,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3105,7 +3125,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3113,7 +3133,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3121,20 +3141,20 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
         <v>35</v>
@@ -3142,7 +3162,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
         <v>36</v>
@@ -3150,7 +3170,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
@@ -3169,7 +3189,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3177,7 +3197,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3186,6 +3206,14 @@
       </c>
       <c r="B13" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>210</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7070"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -145,9 +145,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -161,6 +161,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -170,6 +186,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -196,15 +219,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,29 +243,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -250,29 +252,27 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -290,14 +290,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -330,13 +330,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -348,7 +414,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -366,133 +492,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,11 +506,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -545,21 +551,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -571,9 +562,29 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -592,17 +603,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -611,16 +611,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -632,124 +632,124 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1079,7 +1079,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1285,7 +1285,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B13">
         <v>11</v>
@@ -1302,36 +1302,36 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>252</v>
+        <v>113</v>
       </c>
       <c r="B14">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>1011</v>
+        <v>252</v>
       </c>
       <c r="B15">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1339,36 +1339,33 @@
         <v>1011</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>1011</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
         <v>11010</v>
       </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>1031</v>
-      </c>
-      <c r="B17">
-        <v>61</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1376,16 +1373,16 @@
         <v>1031</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F18" t="s">
         <v>19</v>
@@ -1393,19 +1390,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B19">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F19" t="s">
         <v>19</v>
@@ -1416,209 +1413,209 @@
         <v>1032</v>
       </c>
       <c r="B20">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:6">
       <c r="A21">
+        <v>1032</v>
+      </c>
+      <c r="B21">
+        <v>71</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
         <v>1041</v>
       </c>
-      <c r="B21">
-        <v>61</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="1">
+      <c r="B22">
+        <v>61</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1">
         <v>1041</v>
       </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
         <v>12010</v>
       </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
+    <row r="24" spans="1:5">
+      <c r="A24">
         <v>1042</v>
       </c>
-      <c r="B23">
-        <v>61</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="1">
+      <c r="B24">
+        <v>61</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="1">
         <v>1042</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
         <v>13010</v>
       </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
+    <row r="26" spans="1:5">
+      <c r="A26">
         <v>1051</v>
       </c>
-      <c r="B25">
-        <v>61</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="1">
+      <c r="B26">
+        <v>61</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1">
         <v>1051</v>
       </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
         <v>14050</v>
       </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
+    <row r="28" spans="1:5">
+      <c r="A28">
         <v>1052</v>
       </c>
-      <c r="B27">
-        <v>61</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="1">
-        <v>1052</v>
-      </c>
       <c r="B28">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C28">
-        <v>15010</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1">
+        <v>1052</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>15010</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1">
         <v>1101</v>
       </c>
-      <c r="B29">
-        <v>61</v>
-      </c>
-      <c r="C29">
+      <c r="B30">
+        <v>61</v>
+      </c>
+      <c r="C30">
         <v>4</v>
       </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
         <v>1101</v>
       </c>
-      <c r="B30">
-        <v>2</v>
-      </c>
-      <c r="C30">
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31">
         <v>20</v>
       </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>2041</v>
-      </c>
-      <c r="B31">
-        <v>61</v>
-      </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1626,16 +1623,16 @@
         <v>2041</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C32">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
         <v>22</v>
@@ -1643,19 +1640,19 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B33">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F33" t="s">
         <v>22</v>
@@ -1666,16 +1663,16 @@
         <v>2042</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C34">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
         <v>22</v>
@@ -1686,36 +1683,39 @@
         <v>2042</v>
       </c>
       <c r="B35">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
         <v>20</v>
-      </c>
-      <c r="E35" t="s">
-        <v>21</v>
       </c>
       <c r="F35" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:6">
       <c r="A36">
-        <v>2101</v>
+        <v>2042</v>
       </c>
       <c r="B36">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="F36" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1723,33 +1723,33 @@
         <v>2101</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C37">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="B38">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1757,16 +1757,16 @@
         <v>2102</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C39">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1774,16 +1774,16 @@
         <v>2102</v>
       </c>
       <c r="B40">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1791,7 +1791,7 @@
         <v>2102</v>
       </c>
       <c r="B41">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C41">
         <v>5</v>
@@ -1800,24 +1800,24 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>3041</v>
+        <v>2102</v>
       </c>
       <c r="B42">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1825,33 +1825,33 @@
         <v>3041</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C43">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="B44">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1859,16 +1859,16 @@
         <v>3042</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C45">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1876,33 +1876,33 @@
         <v>3042</v>
       </c>
       <c r="B46">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46" t="s">
         <v>20</v>
-      </c>
-      <c r="E46" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>3101</v>
+        <v>3042</v>
       </c>
       <c r="B47">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1910,33 +1910,33 @@
         <v>3101</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C48">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="B49">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1944,16 +1944,16 @@
         <v>3102</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C50">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1961,16 +1961,16 @@
         <v>3102</v>
       </c>
       <c r="B51">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1978,7 +1978,7 @@
         <v>3102</v>
       </c>
       <c r="B52">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C52">
         <v>5</v>
@@ -1987,24 +1987,24 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>4041</v>
+        <v>3102</v>
       </c>
       <c r="B53">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2012,33 +2012,33 @@
         <v>4041</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C54">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="B55">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2046,16 +2046,16 @@
         <v>4042</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C56">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2063,33 +2063,33 @@
         <v>4042</v>
       </c>
       <c r="B57">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D57">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>4101</v>
+        <v>4042</v>
       </c>
       <c r="B58">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C58">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2097,33 +2097,33 @@
         <v>4101</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C59">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="B60">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2131,16 +2131,16 @@
         <v>4102</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C61">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2148,16 +2148,16 @@
         <v>4102</v>
       </c>
       <c r="B62">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2165,7 +2165,7 @@
         <v>4102</v>
       </c>
       <c r="B63">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C63">
         <v>5</v>
@@ -2174,24 +2174,24 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>5041</v>
+        <v>4102</v>
       </c>
       <c r="B64">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2199,33 +2199,33 @@
         <v>5041</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C65">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>5042</v>
+        <v>5041</v>
       </c>
       <c r="B66">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2233,16 +2233,16 @@
         <v>5042</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C67">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2250,33 +2250,33 @@
         <v>5042</v>
       </c>
       <c r="B68">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D68">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>5101</v>
+        <v>5042</v>
       </c>
       <c r="B69">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E69" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2284,33 +2284,33 @@
         <v>5101</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C70">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="B71">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2318,16 +2318,16 @@
         <v>5102</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C72">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2335,16 +2335,16 @@
         <v>5102</v>
       </c>
       <c r="B73">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2352,7 +2352,7 @@
         <v>5102</v>
       </c>
       <c r="B74">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C74">
         <v>5</v>
@@ -2361,24 +2361,24 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="B75">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2386,33 +2386,33 @@
         <v>6021</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C76">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="B77">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2420,33 +2420,33 @@
         <v>6022</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C78">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="B79">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2454,16 +2454,16 @@
         <v>6031</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C80">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2471,33 +2471,33 @@
         <v>6031</v>
       </c>
       <c r="B81">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D81">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="B82">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C82">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E82" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2505,33 +2505,33 @@
         <v>6101</v>
       </c>
       <c r="B83">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>11020</v>
+        <v>6101</v>
       </c>
       <c r="B84">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2539,33 +2539,33 @@
         <v>11020</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C85">
-        <v>11020</v>
+        <v>1</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="B86">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>11020</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2573,33 +2573,33 @@
         <v>11030</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C87">
-        <v>11030</v>
+        <v>1</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>11040</v>
+        <v>11030</v>
       </c>
       <c r="B88">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>11030</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2607,33 +2607,33 @@
         <v>11040</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C89">
-        <v>11040</v>
+        <v>1</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>12020</v>
+        <v>11040</v>
       </c>
       <c r="B90">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>11040</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2641,33 +2641,33 @@
         <v>12020</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C91">
-        <v>12020</v>
+        <v>1</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>12030</v>
+        <v>12020</v>
       </c>
       <c r="B92">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>12020</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2675,33 +2675,33 @@
         <v>12030</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C93">
-        <v>12030</v>
+        <v>1</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>12040</v>
+        <v>12030</v>
       </c>
       <c r="B94">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>12030</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2709,33 +2709,33 @@
         <v>12040</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C95">
-        <v>12040</v>
+        <v>1</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>13020</v>
+        <v>12040</v>
       </c>
       <c r="B96">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>12040</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2743,33 +2743,33 @@
         <v>13020</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C97">
-        <v>13020</v>
+        <v>1</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>13030</v>
+        <v>13020</v>
       </c>
       <c r="B98">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>13020</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2777,33 +2777,33 @@
         <v>13030</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C99">
-        <v>13030</v>
+        <v>1</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>13040</v>
+        <v>13030</v>
       </c>
       <c r="B100">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>13030</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2811,33 +2811,33 @@
         <v>13040</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C101">
-        <v>13040</v>
+        <v>1</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102">
-        <v>14010</v>
+        <v>13040</v>
       </c>
       <c r="B102">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>13040</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2845,33 +2845,33 @@
         <v>14010</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C103">
-        <v>14010</v>
+        <v>1</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>14020</v>
+        <v>14010</v>
       </c>
       <c r="B104">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>14010</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2879,33 +2879,33 @@
         <v>14020</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C105">
-        <v>14020</v>
+        <v>1</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="B106">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>14020</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2913,33 +2913,33 @@
         <v>14030</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C107">
-        <v>14030</v>
+        <v>1</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>15020</v>
+        <v>14030</v>
       </c>
       <c r="B108">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>14030</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2947,33 +2947,33 @@
         <v>15020</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C109">
-        <v>15020</v>
+        <v>1</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
-        <v>15030</v>
+        <v>15020</v>
       </c>
       <c r="B110">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>15020</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2981,33 +2981,33 @@
         <v>15030</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C111">
-        <v>15030</v>
+        <v>1</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112">
-        <v>15050</v>
+        <v>15030</v>
       </c>
       <c r="B112">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>15030</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3015,41 +3015,41 @@
         <v>15050</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C113">
-        <v>15050</v>
+        <v>1</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114">
-        <v>20010</v>
+        <v>15050</v>
       </c>
       <c r="B114">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>15050</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B115">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -3058,15 +3058,15 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116">
-        <v>20030</v>
+        <v>20020</v>
       </c>
       <c r="B116">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -3075,23 +3075,40 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117">
+        <v>20030</v>
+      </c>
+      <c r="B117">
+        <v>103</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118">
         <v>20040</v>
       </c>
-      <c r="B117">
+      <c r="B118">
         <v>104</v>
       </c>
-      <c r="C117">
-        <v>0</v>
-      </c>
-      <c r="D117">
-        <v>0</v>
-      </c>
-      <c r="E117" t="s">
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118" t="s">
         <v>29</v>
       </c>
     </row>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -74,10 +74,10 @@
     <t>魔法</t>
   </si>
   <si>
+    <t>Nu</t>
+  </si>
+  <si>
     <t>ステージ1中ボス</t>
-  </si>
-  <si>
-    <t>Nu</t>
   </si>
   <si>
     <t>魔法選択</t>
@@ -145,10 +145,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -159,11 +159,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -176,7 +183,22 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -192,7 +214,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -200,6 +222,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -221,25 +251,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -251,30 +265,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -289,8 +282,15 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -312,7 +312,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -324,67 +378,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,85 +444,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -496,6 +460,42 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -503,51 +503,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -571,6 +526,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -580,11 +550,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -603,6 +579,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -611,145 +611,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1079,7 +1079,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1368,23 +1368,20 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:5">
       <c r="A18">
-        <v>1031</v>
+        <v>1021</v>
       </c>
       <c r="B18">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1393,39 +1390,39 @@
         <v>1031</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" t="s">
         <v>20</v>
-      </c>
-      <c r="F19" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B20">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1433,209 +1430,209 @@
         <v>1032</v>
       </c>
       <c r="B21">
+        <v>61</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>1032</v>
+      </c>
+      <c r="B22">
         <v>71</v>
       </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
         <v>10</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E22" t="s">
         <v>21</v>
       </c>
-      <c r="F21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
         <v>1041</v>
       </c>
-      <c r="B22">
-        <v>61</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="1">
+      <c r="B23">
+        <v>61</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1">
         <v>1041</v>
       </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
         <v>12010</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
+    <row r="25" spans="1:5">
+      <c r="A25">
         <v>1042</v>
       </c>
-      <c r="B24">
-        <v>61</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="1">
+      <c r="B25">
+        <v>61</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1">
         <v>1042</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
         <v>13010</v>
       </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
+    <row r="27" spans="1:5">
+      <c r="A27">
         <v>1051</v>
       </c>
-      <c r="B26">
-        <v>61</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="1">
+      <c r="B27">
+        <v>61</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1">
         <v>1051</v>
       </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
         <v>14050</v>
       </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
+    <row r="29" spans="1:5">
+      <c r="A29">
         <v>1052</v>
       </c>
-      <c r="B28">
-        <v>61</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="1">
-        <v>1052</v>
-      </c>
       <c r="B29">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C29">
-        <v>15010</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1">
+        <v>1052</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>15010</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1">
         <v>1101</v>
       </c>
-      <c r="B30">
-        <v>61</v>
-      </c>
-      <c r="C30">
+      <c r="B31">
+        <v>61</v>
+      </c>
+      <c r="C31">
         <v>4</v>
       </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
         <v>1101</v>
       </c>
-      <c r="B31">
-        <v>2</v>
-      </c>
-      <c r="C31">
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32">
         <v>20</v>
       </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>2041</v>
-      </c>
-      <c r="B32">
-        <v>61</v>
-      </c>
-      <c r="C32">
-        <v>2</v>
-      </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1643,16 +1640,16 @@
         <v>2041</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C33">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F33" t="s">
         <v>22</v>
@@ -1660,19 +1657,19 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B34">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F34" t="s">
         <v>22</v>
@@ -1683,16 +1680,16 @@
         <v>2042</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C35">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F35" t="s">
         <v>22</v>
@@ -1703,36 +1700,39 @@
         <v>2042</v>
       </c>
       <c r="B36">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D36">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F36" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:6">
       <c r="A37">
-        <v>2101</v>
+        <v>2042</v>
       </c>
       <c r="B37">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="F37" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1740,33 +1740,33 @@
         <v>2101</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C38">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="B39">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1774,16 +1774,16 @@
         <v>2102</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C40">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1791,16 +1791,16 @@
         <v>2102</v>
       </c>
       <c r="B41">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1808,7 +1808,7 @@
         <v>2102</v>
       </c>
       <c r="B42">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C42">
         <v>5</v>
@@ -1817,24 +1817,24 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>3041</v>
+        <v>2102</v>
       </c>
       <c r="B43">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1842,33 +1842,33 @@
         <v>3041</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C44">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="B45">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1876,16 +1876,16 @@
         <v>3042</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C46">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1893,33 +1893,33 @@
         <v>3042</v>
       </c>
       <c r="B47">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D47">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>3101</v>
+        <v>3042</v>
       </c>
       <c r="B48">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E48" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1927,33 +1927,33 @@
         <v>3101</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C49">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="B50">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1961,16 +1961,16 @@
         <v>3102</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C51">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1978,16 +1978,16 @@
         <v>3102</v>
       </c>
       <c r="B52">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1995,7 +1995,7 @@
         <v>3102</v>
       </c>
       <c r="B53">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>5</v>
@@ -2004,24 +2004,24 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>4041</v>
+        <v>3102</v>
       </c>
       <c r="B54">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2029,33 +2029,33 @@
         <v>4041</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C55">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="B56">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2063,16 +2063,16 @@
         <v>4042</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C57">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2080,33 +2080,33 @@
         <v>4042</v>
       </c>
       <c r="B58">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D58">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>4101</v>
+        <v>4042</v>
       </c>
       <c r="B59">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C59">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E59" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2114,33 +2114,33 @@
         <v>4101</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C60">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="B61">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2148,16 +2148,16 @@
         <v>4102</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C62">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2165,16 +2165,16 @@
         <v>4102</v>
       </c>
       <c r="B63">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2182,7 +2182,7 @@
         <v>4102</v>
       </c>
       <c r="B64">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C64">
         <v>5</v>
@@ -2191,24 +2191,24 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>5041</v>
+        <v>4102</v>
       </c>
       <c r="B65">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2216,33 +2216,33 @@
         <v>5041</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C66">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>5042</v>
+        <v>5041</v>
       </c>
       <c r="B67">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2250,16 +2250,16 @@
         <v>5042</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C68">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2267,33 +2267,33 @@
         <v>5042</v>
       </c>
       <c r="B69">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D69">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>5101</v>
+        <v>5042</v>
       </c>
       <c r="B70">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C70">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E70" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2301,33 +2301,33 @@
         <v>5101</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C71">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="B72">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2335,16 +2335,16 @@
         <v>5102</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C73">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2352,16 +2352,16 @@
         <v>5102</v>
       </c>
       <c r="B74">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2369,7 +2369,7 @@
         <v>5102</v>
       </c>
       <c r="B75">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C75">
         <v>5</v>
@@ -2378,24 +2378,24 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="B76">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2403,33 +2403,33 @@
         <v>6021</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C77">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="B78">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2437,33 +2437,33 @@
         <v>6022</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C79">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="B80">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2471,16 +2471,16 @@
         <v>6031</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C81">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2488,33 +2488,33 @@
         <v>6031</v>
       </c>
       <c r="B82">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D82">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="B83">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C83">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E83" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2522,33 +2522,33 @@
         <v>6101</v>
       </c>
       <c r="B84">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>11020</v>
+        <v>6101</v>
       </c>
       <c r="B85">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2556,33 +2556,33 @@
         <v>11020</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C86">
-        <v>11020</v>
+        <v>1</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="B87">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>11020</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2590,33 +2590,33 @@
         <v>11030</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C88">
-        <v>11030</v>
+        <v>1</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>11040</v>
+        <v>11030</v>
       </c>
       <c r="B89">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>11030</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2624,33 +2624,33 @@
         <v>11040</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C90">
-        <v>11040</v>
+        <v>1</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>12020</v>
+        <v>11040</v>
       </c>
       <c r="B91">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>11040</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2658,33 +2658,33 @@
         <v>12020</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C92">
-        <v>12020</v>
+        <v>1</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>12030</v>
+        <v>12020</v>
       </c>
       <c r="B93">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>12020</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2692,33 +2692,33 @@
         <v>12030</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C94">
-        <v>12030</v>
+        <v>1</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>12040</v>
+        <v>12030</v>
       </c>
       <c r="B95">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>12030</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2726,33 +2726,33 @@
         <v>12040</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C96">
-        <v>12040</v>
+        <v>1</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>13020</v>
+        <v>12040</v>
       </c>
       <c r="B97">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>12040</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2760,33 +2760,33 @@
         <v>13020</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C98">
-        <v>13020</v>
+        <v>1</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>13030</v>
+        <v>13020</v>
       </c>
       <c r="B99">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>13020</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2794,33 +2794,33 @@
         <v>13030</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C100">
-        <v>13030</v>
+        <v>1</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>13040</v>
+        <v>13030</v>
       </c>
       <c r="B101">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>13030</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2828,33 +2828,33 @@
         <v>13040</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C102">
-        <v>13040</v>
+        <v>1</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103">
-        <v>14010</v>
+        <v>13040</v>
       </c>
       <c r="B103">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>13040</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2862,33 +2862,33 @@
         <v>14010</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C104">
-        <v>14010</v>
+        <v>1</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>14020</v>
+        <v>14010</v>
       </c>
       <c r="B105">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>14010</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2896,33 +2896,33 @@
         <v>14020</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C106">
-        <v>14020</v>
+        <v>1</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="B107">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>14020</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2930,33 +2930,33 @@
         <v>14030</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C108">
-        <v>14030</v>
+        <v>1</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109">
-        <v>15020</v>
+        <v>14030</v>
       </c>
       <c r="B109">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>14030</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2964,33 +2964,33 @@
         <v>15020</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C110">
-        <v>15020</v>
+        <v>1</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111">
-        <v>15030</v>
+        <v>15020</v>
       </c>
       <c r="B111">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>15020</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2998,33 +2998,33 @@
         <v>15030</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C112">
-        <v>15030</v>
+        <v>1</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113">
-        <v>15050</v>
+        <v>15030</v>
       </c>
       <c r="B113">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>15030</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3032,41 +3032,41 @@
         <v>15050</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C114">
-        <v>15050</v>
+        <v>1</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115">
-        <v>20010</v>
+        <v>15050</v>
       </c>
       <c r="B115">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>15050</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B116">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -3075,15 +3075,15 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117">
-        <v>20030</v>
+        <v>20020</v>
       </c>
       <c r="B117">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -3092,23 +3092,40 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118">
+        <v>20030</v>
+      </c>
+      <c r="B118">
+        <v>103</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119">
         <v>20040</v>
       </c>
-      <c r="B118">
+      <c r="B119">
         <v>104</v>
       </c>
-      <c r="C118">
-        <v>0</v>
-      </c>
-      <c r="D118">
-        <v>0</v>
-      </c>
-      <c r="E118" t="s">
+      <c r="C119">
+        <v>0</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119" t="s">
         <v>29</v>
       </c>
     </row>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -68,16 +68,16 @@
     <t>選択仲間加入</t>
   </si>
   <si>
+    <t>魔法</t>
+  </si>
+  <si>
     <t>救出</t>
   </si>
   <si>
-    <t>魔法</t>
+    <t>ステージ1中ボス</t>
   </si>
   <si>
     <t>Nu</t>
-  </si>
-  <si>
-    <t>ステージ1中ボス</t>
   </si>
   <si>
     <t>魔法選択</t>
@@ -145,15 +145,52 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -166,8 +203,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -184,14 +259,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -199,75 +267,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -281,16 +281,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -312,7 +312,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -324,13 +342,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -342,7 +366,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -354,31 +402,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -390,13 +414,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -408,31 +462,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -450,49 +486,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -503,6 +503,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -517,11 +532,33 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -543,24 +580,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -579,30 +603,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -611,16 +611,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -629,127 +629,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1079,7 +1079,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1336,13 +1336,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>1011</v>
+        <v>1021</v>
       </c>
       <c r="B16">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>3120</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1351,15 +1351,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:6">
       <c r="A17">
-        <v>1011</v>
+        <v>1031</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C17">
-        <v>11010</v>
+        <v>2</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1367,107 +1367,107 @@
       <c r="E17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
-        <v>1021</v>
+        <v>1031</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B19">
         <v>61</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
         <v>10</v>
       </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
       <c r="E20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
         <v>19</v>
       </c>
-      <c r="F20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21">
-        <v>1032</v>
+        <v>1041</v>
       </c>
       <c r="B21">
         <v>61</v>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="1">
+        <v>1041</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>12010</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
         <v>17</v>
-      </c>
-      <c r="F21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>1032</v>
-      </c>
-      <c r="B22">
-        <v>71</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>10</v>
-      </c>
-      <c r="E22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B23">
         <v>61</v>
@@ -1479,29 +1479,29 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24">
-        <v>12010</v>
+        <v>13010</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>1042</v>
+        <v>1051</v>
       </c>
       <c r="B25">
         <v>61</v>
@@ -1513,29 +1513,29 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1">
-        <v>1042</v>
+        <v>1051</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26">
-        <v>13010</v>
+        <v>14050</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B27">
         <v>61</v>
@@ -1547,80 +1547,83 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
-        <v>14050</v>
+        <v>15010</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29">
-        <v>1052</v>
+      <c r="A29" s="1">
+        <v>1101</v>
       </c>
       <c r="B29">
         <v>61</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="1">
-        <v>1052</v>
+      <c r="A30">
+        <v>1101</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30">
-        <v>15010</v>
+        <v>20</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="1">
-        <v>1101</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>2041</v>
       </c>
       <c r="B31">
         <v>61</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>18</v>
+      </c>
+      <c r="F31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32">
-        <v>1101</v>
+        <v>2041</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -1632,24 +1635,27 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="F32" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B33">
         <v>61</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F33" t="s">
         <v>22</v>
@@ -1657,19 +1663,19 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34">
+        <v>40</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
         <v>20</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34" t="s">
-        <v>19</v>
       </c>
       <c r="F34" t="s">
         <v>22</v>
@@ -1680,64 +1686,58 @@
         <v>2042</v>
       </c>
       <c r="B35">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F35" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:5">
       <c r="A36">
-        <v>2042</v>
+        <v>2101</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C36">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37">
-        <v>2042</v>
+        <v>2101</v>
       </c>
       <c r="B37">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37" t="s">
         <v>20</v>
-      </c>
-      <c r="E37" t="s">
-        <v>21</v>
-      </c>
-      <c r="F37" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B38">
         <v>61</v>
@@ -1749,24 +1749,24 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1774,16 +1774,16 @@
         <v>2102</v>
       </c>
       <c r="B40">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1791,84 +1791,84 @@
         <v>2102</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="C41">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>2102</v>
+        <v>3041</v>
       </c>
       <c r="B42">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>2102</v>
+        <v>3041</v>
       </c>
       <c r="B43">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="B44">
         <v>61</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1876,55 +1876,55 @@
         <v>3042</v>
       </c>
       <c r="B46">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>3042</v>
+        <v>3101</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C47">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>3042</v>
+        <v>3101</v>
       </c>
       <c r="B48">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48" t="s">
         <v>20</v>
-      </c>
-      <c r="E48" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="B49">
         <v>61</v>
@@ -1936,24 +1936,24 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
       <c r="C50">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1961,16 +1961,16 @@
         <v>3102</v>
       </c>
       <c r="B51">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1978,84 +1978,84 @@
         <v>3102</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="C52">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>3102</v>
+        <v>4041</v>
       </c>
       <c r="B53">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>3102</v>
+        <v>4041</v>
       </c>
       <c r="B54">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="B55">
         <v>61</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="B56">
         <v>2</v>
       </c>
       <c r="C56">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2063,55 +2063,55 @@
         <v>4042</v>
       </c>
       <c r="B57">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C57">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E57" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>4042</v>
+        <v>4101</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C58">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>4042</v>
+        <v>4101</v>
       </c>
       <c r="B59">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D59">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>4101</v>
+        <v>4102</v>
       </c>
       <c r="B60">
         <v>61</v>
@@ -2123,24 +2123,24 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>4101</v>
+        <v>4102</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2148,16 +2148,16 @@
         <v>4102</v>
       </c>
       <c r="B62">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2165,84 +2165,84 @@
         <v>4102</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="C63">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>4102</v>
+        <v>5041</v>
       </c>
       <c r="B64">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>4102</v>
+        <v>5041</v>
       </c>
       <c r="B65">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="B66">
         <v>61</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2250,55 +2250,55 @@
         <v>5042</v>
       </c>
       <c r="B68">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E68" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>5042</v>
+        <v>5101</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C69">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>5042</v>
+        <v>5101</v>
       </c>
       <c r="B70">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D70">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="B71">
         <v>61</v>
@@ -2310,24 +2310,24 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2335,16 +2335,16 @@
         <v>5102</v>
       </c>
       <c r="B73">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2352,55 +2352,55 @@
         <v>5102</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="C74">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="B75">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="B76">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="B77">
         <v>61</v>
@@ -2412,12 +2412,12 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -2429,41 +2429,41 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="B79">
         <v>61</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="B80">
         <v>2</v>
       </c>
       <c r="C80">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2471,89 +2471,89 @@
         <v>6031</v>
       </c>
       <c r="B81">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C81">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E81" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C82">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="B83">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>6101</v>
+        <v>11020</v>
       </c>
       <c r="B84">
         <v>61</v>
       </c>
       <c r="C84">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>6101</v>
+        <v>11020</v>
       </c>
       <c r="B85">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>11020</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>11020</v>
+        <v>11030</v>
       </c>
       <c r="B86">
         <v>61</v>
@@ -2565,29 +2565,29 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>11020</v>
+        <v>11030</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87">
-        <v>11020</v>
+        <v>11030</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>11030</v>
+        <v>11040</v>
       </c>
       <c r="B88">
         <v>61</v>
@@ -2599,29 +2599,29 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>11030</v>
+        <v>11040</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89">
-        <v>11030</v>
+        <v>11040</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>11040</v>
+        <v>12020</v>
       </c>
       <c r="B90">
         <v>61</v>
@@ -2633,29 +2633,29 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>11040</v>
+        <v>12020</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91">
-        <v>11040</v>
+        <v>12020</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>12020</v>
+        <v>12030</v>
       </c>
       <c r="B92">
         <v>61</v>
@@ -2667,29 +2667,29 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>12020</v>
+        <v>12030</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>12020</v>
+        <v>12030</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>12030</v>
+        <v>12040</v>
       </c>
       <c r="B94">
         <v>61</v>
@@ -2701,29 +2701,29 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>12030</v>
+        <v>12040</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95">
-        <v>12030</v>
+        <v>12040</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>12040</v>
+        <v>13020</v>
       </c>
       <c r="B96">
         <v>61</v>
@@ -2735,29 +2735,29 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>12040</v>
+        <v>13020</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>12040</v>
+        <v>13020</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>13020</v>
+        <v>13030</v>
       </c>
       <c r="B98">
         <v>61</v>
@@ -2769,29 +2769,29 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>13020</v>
+        <v>13030</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99">
-        <v>13020</v>
+        <v>13030</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>13030</v>
+        <v>13040</v>
       </c>
       <c r="B100">
         <v>61</v>
@@ -2803,29 +2803,29 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>13030</v>
+        <v>13040</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>13030</v>
+        <v>13040</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102">
-        <v>13040</v>
+        <v>14010</v>
       </c>
       <c r="B102">
         <v>61</v>
@@ -2837,29 +2837,29 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103">
-        <v>13040</v>
+        <v>14010</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>13040</v>
+        <v>14010</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>14010</v>
+        <v>14020</v>
       </c>
       <c r="B104">
         <v>61</v>
@@ -2871,29 +2871,29 @@
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>14010</v>
+        <v>14020</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>14010</v>
+        <v>14020</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>14020</v>
+        <v>14030</v>
       </c>
       <c r="B106">
         <v>61</v>
@@ -2905,29 +2905,29 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>14020</v>
+        <v>14030</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>14020</v>
+        <v>14030</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>14030</v>
+        <v>15020</v>
       </c>
       <c r="B108">
         <v>61</v>
@@ -2939,29 +2939,29 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109">
-        <v>14030</v>
+        <v>15020</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>14030</v>
+        <v>15020</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
-        <v>15020</v>
+        <v>15030</v>
       </c>
       <c r="B110">
         <v>61</v>
@@ -2973,29 +2973,29 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111">
-        <v>15020</v>
+        <v>15030</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>15020</v>
+        <v>15030</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112">
-        <v>15030</v>
+        <v>15050</v>
       </c>
       <c r="B112">
         <v>61</v>
@@ -3007,66 +3007,66 @@
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113">
-        <v>15030</v>
+        <v>15050</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>15030</v>
+        <v>15050</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114">
-        <v>15050</v>
+        <v>20010</v>
       </c>
       <c r="B114">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115">
-        <v>15050</v>
+        <v>20020</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="C115">
-        <v>15050</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116">
-        <v>20010</v>
+        <v>20030</v>
       </c>
       <c r="B116">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -3075,15 +3075,15 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117">
-        <v>20020</v>
+        <v>20040</v>
       </c>
       <c r="B117">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -3092,40 +3092,6 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
-      <c r="A118">
-        <v>20030</v>
-      </c>
-      <c r="B118">
-        <v>103</v>
-      </c>
-      <c r="C118">
-        <v>0</v>
-      </c>
-      <c r="D118">
-        <v>0</v>
-      </c>
-      <c r="E118" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
-      <c r="A119">
-        <v>20040</v>
-      </c>
-      <c r="B119">
-        <v>104</v>
-      </c>
-      <c r="C119">
-        <v>0</v>
-      </c>
-      <c r="D119">
-        <v>0</v>
-      </c>
-      <c r="E119" t="s">
         <v>29</v>
       </c>
     </row>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="40">
   <si>
     <t>Id</t>
   </si>
@@ -71,19 +71,16 @@
     <t>魔法</t>
   </si>
   <si>
+    <t>魔法選択</t>
+  </si>
+  <si>
     <t>救出</t>
   </si>
   <si>
-    <t>ステージ1中ボス</t>
+    <t>ステージ2中ボス</t>
   </si>
   <si>
     <t>Nu</t>
-  </si>
-  <si>
-    <t>魔法選択</t>
-  </si>
-  <si>
-    <t>ステージ2中ボス</t>
   </si>
   <si>
     <t>Nu獲得量アップ</t>
@@ -146,8 +143,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -160,21 +157,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -182,29 +172,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,15 +211,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,9 +225,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -259,15 +256,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -281,16 +270,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -312,6 +309,72 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -324,7 +387,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -336,163 +489,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -503,6 +500,36 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -521,11 +548,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -548,32 +581,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -588,21 +600,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -611,7 +608,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -620,7 +617,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -629,76 +626,106 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -707,49 +734,19 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1079,7 +1076,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1351,430 +1348,418 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:5">
       <c r="A17">
-        <v>1031</v>
+        <v>1041</v>
       </c>
       <c r="B17">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>1101</v>
+      </c>
+      <c r="B18">
+        <v>71</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
         <v>18</v>
-      </c>
-      <c r="F17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>1031</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-      <c r="C18">
-        <v>10</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>1032</v>
+        <v>2041</v>
       </c>
       <c r="B19">
         <v>61</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>1032</v>
+        <v>2041</v>
       </c>
       <c r="B20">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E20" t="s">
         <v>21</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
-        <v>1041</v>
+        <v>2042</v>
       </c>
       <c r="B21">
         <v>61</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="1">
-        <v>1041</v>
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>2042</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>12010</v>
+        <v>40</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
-        <v>1042</v>
+        <v>2042</v>
       </c>
       <c r="B23">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E23" t="s">
         <v>18</v>
       </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="1">
-        <v>1042</v>
+      <c r="A24">
+        <v>2101</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C24">
-        <v>13010</v>
+        <v>4</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>1051</v>
+        <v>2101</v>
       </c>
       <c r="B25">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="1">
-        <v>1051</v>
+      <c r="A26">
+        <v>2102</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C26">
-        <v>14050</v>
+        <v>4</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>1052</v>
+        <v>2102</v>
       </c>
       <c r="B27">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="1">
-        <v>1052</v>
+      <c r="A28">
+        <v>2102</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="C28">
-        <v>15010</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="1">
-        <v>1101</v>
+      <c r="A29">
+        <v>2102</v>
       </c>
       <c r="B29">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>1101</v>
+        <v>3041</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>3041</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31">
+        <v>30</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>3042</v>
+      </c>
+      <c r="B32">
+        <v>61</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>3042</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33">
+        <v>50</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>3042</v>
+      </c>
+      <c r="B34">
+        <v>71</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
         <v>20</v>
       </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>2041</v>
-      </c>
-      <c r="B31">
-        <v>61</v>
-      </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="E34" t="s">
         <v>18</v>
       </c>
-      <c r="F31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>2041</v>
-      </c>
-      <c r="B32">
-        <v>2</v>
-      </c>
-      <c r="C32">
-        <v>20</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32" t="s">
-        <v>20</v>
-      </c>
-      <c r="F32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>2042</v>
-      </c>
-      <c r="B33">
-        <v>61</v>
-      </c>
-      <c r="C33">
-        <v>3</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33" t="s">
-        <v>18</v>
-      </c>
-      <c r="F33" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>2042</v>
-      </c>
-      <c r="B34">
-        <v>2</v>
-      </c>
-      <c r="C34">
-        <v>40</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34" t="s">
-        <v>20</v>
-      </c>
-      <c r="F34" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35">
-        <v>2042</v>
+        <v>3101</v>
       </c>
       <c r="B35">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
-      </c>
-      <c r="F35" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>2101</v>
+        <v>3101</v>
       </c>
       <c r="B36">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>2101</v>
+        <v>3102</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C37">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>2102</v>
+        <v>3102</v>
       </c>
       <c r="B38">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>2102</v>
+        <v>3102</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="C39">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>2102</v>
+        <v>3102</v>
       </c>
       <c r="B40">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>5</v>
@@ -1788,180 +1773,180 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>2102</v>
+        <v>4041</v>
       </c>
       <c r="B41">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>3041</v>
+        <v>4041</v>
       </c>
       <c r="B42">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>3041</v>
+        <v>4042</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C43">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>3042</v>
+        <v>4042</v>
       </c>
       <c r="B44">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>3042</v>
+        <v>4042</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="C45">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E45" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>3042</v>
+        <v>4101</v>
       </c>
       <c r="B46">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D46">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>3101</v>
+        <v>4101</v>
       </c>
       <c r="B47">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>3101</v>
+        <v>4102</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C48">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>3102</v>
+        <v>4102</v>
       </c>
       <c r="B49">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>3102</v>
+        <v>4102</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="C50">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>3102</v>
+        <v>4102</v>
       </c>
       <c r="B51">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C51">
         <v>5</v>
@@ -1975,180 +1960,180 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>3102</v>
+        <v>5041</v>
       </c>
       <c r="B52">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C52">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>4041</v>
+        <v>5041</v>
       </c>
       <c r="B53">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>4041</v>
+        <v>5042</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C54">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>4042</v>
+        <v>5042</v>
       </c>
       <c r="B55">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>4042</v>
+        <v>5042</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="C56">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E56" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>4042</v>
+        <v>5101</v>
       </c>
       <c r="B57">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D57">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>4101</v>
+        <v>5101</v>
       </c>
       <c r="B58">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>4101</v>
+        <v>5102</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C59">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>4102</v>
+        <v>5102</v>
       </c>
       <c r="B60">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>4102</v>
+        <v>5102</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="C61">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>4102</v>
+        <v>5102</v>
       </c>
       <c r="B62">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C62">
         <v>5</v>
@@ -2162,101 +2147,101 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>4102</v>
+        <v>6021</v>
       </c>
       <c r="B63">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>5041</v>
+        <v>6021</v>
       </c>
       <c r="B64">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>5041</v>
+        <v>6022</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C65">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>5042</v>
+        <v>6022</v>
       </c>
       <c r="B66">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>5042</v>
+        <v>6031</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C67">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>5042</v>
+        <v>6031</v>
       </c>
       <c r="B68">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D68">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E68" t="s">
         <v>21</v>
@@ -2264,16 +2249,16 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>5101</v>
+        <v>6031</v>
       </c>
       <c r="B69">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="E69" t="s">
         <v>18</v>
@@ -2281,245 +2266,245 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>5101</v>
+        <v>6101</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C70">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>5102</v>
+        <v>6101</v>
       </c>
       <c r="B71">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="C71">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>5102</v>
+        <v>11020</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C72">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>5102</v>
+        <v>11020</v>
       </c>
       <c r="B73">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>5</v>
+        <v>11020</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>5102</v>
+        <v>11030</v>
       </c>
       <c r="B74">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>6021</v>
+        <v>11030</v>
       </c>
       <c r="B75">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>11030</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>6021</v>
+        <v>11040</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C76">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>6022</v>
+        <v>11040</v>
       </c>
       <c r="B77">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>11040</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>6022</v>
+        <v>12020</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C78">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>6031</v>
+        <v>12020</v>
       </c>
       <c r="B79">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>4</v>
+        <v>12020</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>6031</v>
+        <v>12030</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C80">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>6031</v>
+        <v>12030</v>
       </c>
       <c r="B81">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>12030</v>
       </c>
       <c r="D81">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>6101</v>
+        <v>12040</v>
       </c>
       <c r="B82">
         <v>61</v>
       </c>
       <c r="C82">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>6101</v>
+        <v>12040</v>
       </c>
       <c r="B83">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>12040</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>11020</v>
+        <v>13020</v>
       </c>
       <c r="B84">
         <v>61</v>
@@ -2531,18 +2516,18 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>11020</v>
+        <v>13020</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>11020</v>
+        <v>13020</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2553,7 +2538,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>11030</v>
+        <v>13030</v>
       </c>
       <c r="B86">
         <v>61</v>
@@ -2565,18 +2550,18 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>11030</v>
+        <v>13030</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87">
-        <v>11030</v>
+        <v>13030</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2587,7 +2572,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>11040</v>
+        <v>13040</v>
       </c>
       <c r="B88">
         <v>61</v>
@@ -2599,18 +2584,18 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>11040</v>
+        <v>13040</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89">
-        <v>11040</v>
+        <v>13040</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -2621,7 +2606,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>12020</v>
+        <v>14010</v>
       </c>
       <c r="B90">
         <v>61</v>
@@ -2633,18 +2618,18 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>12020</v>
+        <v>14010</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91">
-        <v>12020</v>
+        <v>14010</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -2655,7 +2640,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>12030</v>
+        <v>14020</v>
       </c>
       <c r="B92">
         <v>61</v>
@@ -2667,18 +2652,18 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>12030</v>
+        <v>14020</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>12030</v>
+        <v>14020</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -2689,7 +2674,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>12040</v>
+        <v>14030</v>
       </c>
       <c r="B94">
         <v>61</v>
@@ -2701,18 +2686,18 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>12040</v>
+        <v>14030</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95">
-        <v>12040</v>
+        <v>14030</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -2723,7 +2708,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>13020</v>
+        <v>15020</v>
       </c>
       <c r="B96">
         <v>61</v>
@@ -2735,18 +2720,18 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>13020</v>
+        <v>15020</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>13020</v>
+        <v>15020</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -2757,7 +2742,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>13030</v>
+        <v>15030</v>
       </c>
       <c r="B98">
         <v>61</v>
@@ -2769,18 +2754,18 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>13030</v>
+        <v>15030</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99">
-        <v>13030</v>
+        <v>15030</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -2791,7 +2776,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>13040</v>
+        <v>15050</v>
       </c>
       <c r="B100">
         <v>61</v>
@@ -2803,18 +2788,18 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>13040</v>
+        <v>15050</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>13040</v>
+        <v>15050</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -2825,274 +2810,70 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102">
-        <v>14010</v>
+        <v>20010</v>
       </c>
       <c r="B102">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103">
-        <v>14010</v>
+        <v>20020</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="C103">
-        <v>14010</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>14020</v>
+        <v>20030</v>
       </c>
       <c r="B104">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>14020</v>
+        <v>20040</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="C105">
-        <v>14020</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106">
-        <v>14030</v>
-      </c>
-      <c r="B106">
-        <v>61</v>
-      </c>
-      <c r="C106">
-        <v>1</v>
-      </c>
-      <c r="D106">
-        <v>0</v>
-      </c>
-      <c r="E106" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107">
-        <v>14030</v>
-      </c>
-      <c r="B107">
-        <v>1</v>
-      </c>
-      <c r="C107">
-        <v>14030</v>
-      </c>
-      <c r="D107">
-        <v>0</v>
-      </c>
-      <c r="E107" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108">
-        <v>15020</v>
-      </c>
-      <c r="B108">
-        <v>61</v>
-      </c>
-      <c r="C108">
-        <v>1</v>
-      </c>
-      <c r="D108">
-        <v>0</v>
-      </c>
-      <c r="E108" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109">
-        <v>15020</v>
-      </c>
-      <c r="B109">
-        <v>1</v>
-      </c>
-      <c r="C109">
-        <v>15020</v>
-      </c>
-      <c r="D109">
-        <v>0</v>
-      </c>
-      <c r="E109" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110">
-        <v>15030</v>
-      </c>
-      <c r="B110">
-        <v>61</v>
-      </c>
-      <c r="C110">
-        <v>1</v>
-      </c>
-      <c r="D110">
-        <v>0</v>
-      </c>
-      <c r="E110" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111">
-        <v>15030</v>
-      </c>
-      <c r="B111">
-        <v>1</v>
-      </c>
-      <c r="C111">
-        <v>15030</v>
-      </c>
-      <c r="D111">
-        <v>0</v>
-      </c>
-      <c r="E111" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112">
-        <v>15050</v>
-      </c>
-      <c r="B112">
-        <v>61</v>
-      </c>
-      <c r="C112">
-        <v>1</v>
-      </c>
-      <c r="D112">
-        <v>0</v>
-      </c>
-      <c r="E112" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113">
-        <v>15050</v>
-      </c>
-      <c r="B113">
-        <v>1</v>
-      </c>
-      <c r="C113">
-        <v>15050</v>
-      </c>
-      <c r="D113">
-        <v>0</v>
-      </c>
-      <c r="E113" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114">
-        <v>20010</v>
-      </c>
-      <c r="B114">
-        <v>101</v>
-      </c>
-      <c r="C114">
-        <v>0</v>
-      </c>
-      <c r="D114">
-        <v>0</v>
-      </c>
-      <c r="E114" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115">
-        <v>20020</v>
-      </c>
-      <c r="B115">
-        <v>102</v>
-      </c>
-      <c r="C115">
-        <v>0</v>
-      </c>
-      <c r="D115">
-        <v>0</v>
-      </c>
-      <c r="E115" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116">
-        <v>20030</v>
-      </c>
-      <c r="B116">
-        <v>103</v>
-      </c>
-      <c r="C116">
-        <v>0</v>
-      </c>
-      <c r="D116">
-        <v>0</v>
-      </c>
-      <c r="E116" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
-      <c r="A117">
-        <v>20040</v>
-      </c>
-      <c r="B117">
-        <v>104</v>
-      </c>
-      <c r="C117">
-        <v>0</v>
-      </c>
-      <c r="D117">
-        <v>0</v>
-      </c>
-      <c r="E117" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3109,7 +2890,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3117,7 +2898,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3125,7 +2906,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3133,7 +2914,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3141,7 +2922,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3157,7 +2938,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3165,7 +2946,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3173,7 +2954,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3181,7 +2962,7 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3189,7 +2970,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3197,7 +2978,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3205,7 +2986,7 @@
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3213,7 +2994,7 @@
         <v>210</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
